--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T08:19:41+00:00</t>
+          <t>2026-06-09T10:57:52+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T10:57:52+00:00</t>
+          <t>2026-06-09T16:55:07+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:07+00:00</t>
+          <t>2026-06-09T19:08:16+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T19:08:16+00:00</t>
+          <t>2026-06-09T19:50:56+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T19:50:56+00:00</t>
+          <t>2026-06-09T20:50:32+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T20:50:32+00:00</t>
+          <t>2026-06-09T21:53:56+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T16:55:07+00:00</t>
+          <t>2026-06-09T22:25:18+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T22:25:18+00:00</t>
+          <t>2026-06-09T23:12:24+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:24+00:00</t>
+          <t>2026-06-09T23:31:17+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:31:17+00:00</t>
+          <t>2026-06-10T01:08:53+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T01:08:53+00:00</t>
+          <t>2026-06-10T01:48:56+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T01:48:56+00:00</t>
+          <t>2026-06-10T05:56:10+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T05:56:10+00:00</t>
+          <t>2026-06-10T07:53:51+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T07:53:51+00:00</t>
+          <t>2026-06-10T10:52:04+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-09T23:12:24+00:00</t>
+          <t>2026-06-10T10:52:04+00:00</t>
         </is>
       </c>
     </row>

--- a/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
+++ b/settlements/obex/2026-03/obex_settlement_march_2026.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-06-10T10:52:04+00:00</t>
+          <t>2026-07-03T07:03:01+00:00</t>
         </is>
       </c>
     </row>
